--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -933,13 +933,13 @@
         <v>29.41</v>
       </c>
       <c r="I11" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3245,13 +3245,13 @@
         <v>29.41</v>
       </c>
       <c r="I11" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -883,19 +883,19 @@
         <v>54</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>73.81</v>
+        <v>74.42</v>
       </c>
       <c r="H10" s="1">
-        <v>26.19</v>
+        <v>25.58</v>
       </c>
       <c r="I10" s="2">
         <v>7.2</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -956,22 +956,25 @@
         <v>15</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1020,28 +1023,28 @@
         <v>55</v>
       </c>
       <c r="D14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14">
         <v>28</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>82.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="H14" s="1">
-        <v>17.65</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1058,25 +1061,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>71.05</v>
+        <v>78.95</v>
       </c>
       <c r="H15" s="1">
-        <v>28.95</v>
+        <v>21.05</v>
       </c>
       <c r="I15" s="2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J15">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1105,13 +1108,13 @@
         <v>34.62</v>
       </c>
       <c r="I16" s="2">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1128,25 +1131,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>78.13</v>
+        <v>84.38</v>
       </c>
       <c r="H17" s="1">
-        <v>21.88</v>
+        <v>15.63</v>
       </c>
       <c r="I17" s="2">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1210,7 +1213,7 @@
         <v>17.14</v>
       </c>
       <c r="I19" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1475,28 +1478,28 @@
         <v>55</v>
       </c>
       <c r="D27">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27">
+        <v>19</v>
+      </c>
+      <c r="F27">
         <v>12</v>
       </c>
-      <c r="F27">
-        <v>20</v>
-      </c>
       <c r="G27" s="1">
-        <v>37.5</v>
+        <v>61.29</v>
       </c>
       <c r="H27" s="1">
-        <v>62.5</v>
+        <v>38.71</v>
       </c>
       <c r="I27" s="2">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1580,22 +1583,22 @@
         <v>54</v>
       </c>
       <c r="D30">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E30">
         <v>26</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H30" s="1">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="I30" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1650,19 +1653,19 @@
         <v>54</v>
       </c>
       <c r="D32">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E32">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32">
         <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>78.05</v>
+        <v>77.5</v>
       </c>
       <c r="H32" s="1">
-        <v>21.95</v>
+        <v>22.5</v>
       </c>
       <c r="I32" s="2">
         <v>6.9</v>
@@ -1671,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="K32" s="1">
-        <v>21.95</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1842,22 +1845,25 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>34.62</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1938,22 +1944,25 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>22.22</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2063,13 +2072,13 @@
         <v>54</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2078,7 +2087,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -2191,25 +2200,28 @@
         <v>55</v>
       </c>
       <c r="D14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>25.71</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2226,22 +2238,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>18.42</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.4</v>
       </c>
       <c r="J15">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2258,22 +2273,25 @@
         <v>26</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F16">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>69.23</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>30.77</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6.5</v>
       </c>
       <c r="J16">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2290,22 +2308,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>21.88</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2322,22 +2343,25 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>25.81</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6.6</v>
       </c>
       <c r="J18">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2354,22 +2378,25 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>25.71</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.1</v>
       </c>
       <c r="J19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2386,22 +2413,25 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>4.76</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6.6</v>
       </c>
       <c r="J20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2418,22 +2448,25 @@
         <v>37</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F21">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>94.59</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>5.41</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.4</v>
       </c>
       <c r="J21">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2450,22 +2483,25 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F22">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I22" s="2">
+        <v>6.9</v>
       </c>
       <c r="J22">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2482,22 +2518,25 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>31.25</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.4</v>
       </c>
       <c r="J23">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2514,22 +2553,25 @@
         <v>32</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F24">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>31.25</v>
+      </c>
+      <c r="I24" s="2">
+        <v>6.4</v>
       </c>
       <c r="J24">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2546,22 +2588,25 @@
         <v>41</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F25">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>51.22</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>48.78</v>
+      </c>
+      <c r="I25" s="2">
+        <v>5.7</v>
       </c>
       <c r="J25">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2578,22 +2623,25 @@
         <v>39</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F26">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>38.46</v>
+      </c>
+      <c r="I26" s="2">
+        <v>6.1</v>
       </c>
       <c r="J26">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2607,25 +2655,28 @@
         <v>55</v>
       </c>
       <c r="D27">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>58.06</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>41.94</v>
+      </c>
+      <c r="I27" s="2">
+        <v>6.2</v>
       </c>
       <c r="J27">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2703,13 +2754,13 @@
         <v>54</v>
       </c>
       <c r="D30">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -2718,7 +2769,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K30" s="1">
         <v>100</v>
@@ -2767,13 +2818,13 @@
         <v>54</v>
       </c>
       <c r="D32">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -2782,7 +2833,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -2953,19 +3004,19 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>50</v>
+        <v>65.38</v>
       </c>
       <c r="H3" s="1">
-        <v>50</v>
+        <v>34.62</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3058,19 +3109,19 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H6" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3195,19 +3246,19 @@
         <v>54</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>73.81</v>
+        <v>74.42</v>
       </c>
       <c r="H10" s="1">
-        <v>26.19</v>
+        <v>25.58</v>
       </c>
       <c r="I10" s="2">
         <v>7.2</v>
@@ -3216,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3268,22 +3319,25 @@
         <v>15</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3332,28 +3386,28 @@
         <v>55</v>
       </c>
       <c r="D14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>82.34999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>17.65</v>
+        <v>25.71</v>
       </c>
       <c r="I14" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3370,25 +3424,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>71.05</v>
+        <v>81.58</v>
       </c>
       <c r="H15" s="1">
-        <v>28.95</v>
+        <v>18.42</v>
       </c>
       <c r="I15" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3405,25 +3459,25 @@
         <v>26</v>
       </c>
       <c r="E16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
-        <v>65.38</v>
+        <v>69.23</v>
       </c>
       <c r="H16" s="1">
-        <v>34.62</v>
+        <v>30.77</v>
       </c>
       <c r="I16" s="2">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="J16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3452,13 +3506,13 @@
         <v>21.88</v>
       </c>
       <c r="I17" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3487,7 +3541,7 @@
         <v>25.81</v>
       </c>
       <c r="I18" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3510,19 +3564,19 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>82.86</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>17.14</v>
+        <v>25.71</v>
       </c>
       <c r="I19" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3545,16 +3599,16 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I20" s="2">
         <v>6.7</v>
@@ -3592,7 +3646,7 @@
         <v>5.41</v>
       </c>
       <c r="I21" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -3627,7 +3681,7 @@
         <v>16.67</v>
       </c>
       <c r="I22" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3662,7 +3716,7 @@
         <v>31.25</v>
       </c>
       <c r="I23" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -3685,19 +3739,19 @@
         <v>32</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1">
-        <v>78.13</v>
+        <v>68.75</v>
       </c>
       <c r="H24" s="1">
-        <v>21.88</v>
+        <v>31.25</v>
       </c>
       <c r="I24" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3720,19 +3774,19 @@
         <v>41</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G25" s="1">
-        <v>70.73</v>
+        <v>51.22</v>
       </c>
       <c r="H25" s="1">
-        <v>29.27</v>
+        <v>48.78</v>
       </c>
       <c r="I25" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3755,19 +3809,19 @@
         <v>39</v>
       </c>
       <c r="E26">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G26" s="1">
-        <v>74.36</v>
+        <v>61.54</v>
       </c>
       <c r="H26" s="1">
-        <v>25.64</v>
+        <v>38.46</v>
       </c>
       <c r="I26" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3787,28 +3841,28 @@
         <v>55</v>
       </c>
       <c r="D27">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G27" s="1">
-        <v>37.5</v>
+        <v>58.06</v>
       </c>
       <c r="H27" s="1">
-        <v>62.5</v>
+        <v>41.94</v>
       </c>
       <c r="I27" s="2">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="J27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3892,22 +3946,22 @@
         <v>54</v>
       </c>
       <c r="D30">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E30">
         <v>26</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H30" s="1">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="I30" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -3962,19 +4016,19 @@
         <v>54</v>
       </c>
       <c r="D32">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E32">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32">
         <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>78.05</v>
+        <v>77.5</v>
       </c>
       <c r="H32" s="1">
-        <v>21.95</v>
+        <v>22.5</v>
       </c>
       <c r="I32" s="2">
         <v>6.9</v>
@@ -3983,7 +4037,7 @@
         <v>9</v>
       </c>
       <c r="K32" s="1">
-        <v>21.95</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="33" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -1813,22 +1813,25 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>38.46</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.1</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1880,22 +1883,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>42.11</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1912,22 +1918,25 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>35.29</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1979,22 +1988,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.3</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2011,22 +2023,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>15.91</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2043,22 +2058,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>23.26</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.7</v>
       </c>
       <c r="J9">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2075,22 +2093,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>25.58</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.4</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2107,22 +2128,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>35.29</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.7</v>
       </c>
       <c r="J11">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2171,22 +2195,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2693,22 +2720,25 @@
         <v>39</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>51.28</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>48.72</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.8</v>
       </c>
       <c r="J28">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2969,19 +2999,19 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>80.77</v>
+        <v>61.54</v>
       </c>
       <c r="H2" s="1">
-        <v>19.23</v>
+        <v>38.46</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3039,19 +3069,19 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>52.63</v>
+        <v>57.89</v>
       </c>
       <c r="H4" s="1">
-        <v>47.37</v>
+        <v>42.11</v>
       </c>
       <c r="I4" s="2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -3074,19 +3104,19 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
-        <v>50</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>50</v>
+        <v>32.35</v>
       </c>
       <c r="I5" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -3144,19 +3174,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="H7" s="1">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3191,7 +3221,7 @@
         <v>15.91</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3214,19 +3244,19 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>79.06999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>20.93</v>
+        <v>23.26</v>
       </c>
       <c r="I9" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3261,7 +3291,7 @@
         <v>25.58</v>
       </c>
       <c r="I10" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -3284,19 +3314,19 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>70.59</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>29.41</v>
+        <v>35.29</v>
       </c>
       <c r="I11" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3354,19 +3384,19 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>86.11</v>
+        <v>83.33</v>
       </c>
       <c r="H13" s="1">
-        <v>13.89</v>
+        <v>16.67</v>
       </c>
       <c r="I13" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -3879,19 +3909,19 @@
         <v>39</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1">
-        <v>56.41</v>
+        <v>51.28</v>
       </c>
       <c r="H28" s="1">
-        <v>43.59</v>
+        <v>48.72</v>
       </c>
       <c r="I28" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>17</v>

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -2163,22 +2163,25 @@
         <v>15</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>46.67</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.3</v>
       </c>
       <c r="J12">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2755,22 +2758,25 @@
         <v>34</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F29">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>11.76</v>
+      </c>
+      <c r="I29" s="2">
+        <v>7.4</v>
       </c>
       <c r="J29">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2851,22 +2857,25 @@
         <v>40</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="I32" s="2">
+        <v>6.5</v>
       </c>
       <c r="J32">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2883,22 +2892,25 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F33">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.2</v>
       </c>
       <c r="J33">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2915,22 +2927,25 @@
         <v>44</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F34">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>86.36</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>13.64</v>
+      </c>
+      <c r="I34" s="2">
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3349,16 +3364,16 @@
         <v>15</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>60</v>
+        <v>53.33</v>
       </c>
       <c r="H12" s="1">
-        <v>40</v>
+        <v>46.67</v>
       </c>
       <c r="I12" s="2">
         <v>6.4</v>
@@ -3944,19 +3959,19 @@
         <v>34</v>
       </c>
       <c r="E29">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>14.71</v>
+        <v>11.76</v>
       </c>
       <c r="I29" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4084,16 +4099,16 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H33" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I33" s="2">
         <v>7.3</v>
@@ -4119,19 +4134,19 @@
         <v>44</v>
       </c>
       <c r="E34">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G34" s="1">
-        <v>93.18000000000001</v>
+        <v>86.36</v>
       </c>
       <c r="H34" s="1">
-        <v>6.82</v>
+        <v>13.64</v>
       </c>
       <c r="I34" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J34">
         <v>0</v>

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -2793,22 +2793,25 @@
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F30">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I30" s="2">
+        <v>6.6</v>
       </c>
       <c r="J30">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2825,22 +2828,25 @@
         <v>41</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F31">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>78.05</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>21.95</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6.4</v>
       </c>
       <c r="J31">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2857,25 +2863,25 @@
         <v>40</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F32">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="H32" s="1">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="I32" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="K32" s="1">
-        <v>95</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3994,19 +4000,19 @@
         <v>30</v>
       </c>
       <c r="E30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
-        <v>86.67</v>
+        <v>83.33</v>
       </c>
       <c r="H30" s="1">
-        <v>13.33</v>
+        <v>16.67</v>
       </c>
       <c r="I30" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4029,16 +4035,16 @@
         <v>41</v>
       </c>
       <c r="E31">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>80.48999999999999</v>
+        <v>78.05</v>
       </c>
       <c r="H31" s="1">
-        <v>19.51</v>
+        <v>21.95</v>
       </c>
       <c r="I31" s="2">
         <v>6.6</v>
@@ -4064,19 +4070,19 @@
         <v>40</v>
       </c>
       <c r="E32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="H32" s="1">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="I32" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J32">
         <v>9</v>

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -656,10 +656,10 @@
         <v>6.2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -676,25 +676,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>52.63</v>
+        <v>57.89</v>
       </c>
       <c r="H4" s="1">
-        <v>47.37</v>
+        <v>42.11</v>
       </c>
       <c r="I4" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -723,13 +723,13 @@
         <v>50</v>
       </c>
       <c r="I5" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -886,25 +886,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>25.58</v>
+        <v>23.26</v>
       </c>
       <c r="I10" s="2">
         <v>7.2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -921,25 +921,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>70.59</v>
+        <v>73.53</v>
       </c>
       <c r="H11" s="1">
-        <v>29.41</v>
+        <v>26.47</v>
       </c>
       <c r="I11" s="2">
         <v>6.6</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1003,13 +1003,13 @@
         <v>13.89</v>
       </c>
       <c r="I13" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1026,19 +1026,19 @@
         <v>35</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H14" s="1">
-        <v>20</v>
+        <v>17.14</v>
       </c>
       <c r="I14" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1633,13 +1633,13 @@
         <v>19.51</v>
       </c>
       <c r="I31" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>7.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1656,25 +1656,25 @@
         <v>40</v>
       </c>
       <c r="E32">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G32" s="1">
-        <v>77.5</v>
+        <v>80</v>
       </c>
       <c r="H32" s="1">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="I32" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1863,10 +1863,10 @@
         <v>7</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1883,25 +1883,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>57.89</v>
+        <v>63.16</v>
       </c>
       <c r="H4" s="1">
-        <v>42.11</v>
+        <v>36.84</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1918,25 +1918,25 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>35.29</v>
+        <v>32.35</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>20.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2093,25 +2093,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>25.58</v>
+        <v>23.26</v>
       </c>
       <c r="I10" s="2">
         <v>6.4</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2128,25 +2128,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>35.29</v>
+        <v>32.35</v>
       </c>
       <c r="I11" s="2">
         <v>6.7</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2198,25 +2198,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H13" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2828,25 +2828,25 @@
         <v>41</v>
       </c>
       <c r="E31">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G31" s="1">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>21.95</v>
+        <v>17.07</v>
       </c>
       <c r="I31" s="2">
         <v>6.4</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>7.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2863,25 +2863,25 @@
         <v>40</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G32" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H32" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I32" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3067,13 +3067,13 @@
         <v>34.62</v>
       </c>
       <c r="I3" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3090,25 +3090,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>57.89</v>
+        <v>63.16</v>
       </c>
       <c r="H4" s="1">
-        <v>42.11</v>
+        <v>36.84</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3137,13 +3137,13 @@
         <v>32.35</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3300,25 +3300,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>25.58</v>
+        <v>23.26</v>
       </c>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3335,25 +3335,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>35.29</v>
+        <v>32.35</v>
       </c>
       <c r="I11" s="2">
         <v>6.7</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3405,25 +3405,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H13" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4035,25 +4035,25 @@
         <v>41</v>
       </c>
       <c r="E31">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G31" s="1">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>21.95</v>
+        <v>17.07</v>
       </c>
       <c r="I31" s="2">
         <v>6.6</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>7.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4070,25 +4070,25 @@
         <v>40</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G32" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H32" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I32" s="2">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="J32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -1271,25 +1271,25 @@
         <v>37</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1341,25 +1341,25 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2478,25 +2478,25 @@
         <v>37</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
         <v>7.4</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2548,25 +2548,25 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3685,25 +3685,25 @@
         <v>37</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
         <v>7.5</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3755,25 +3755,25 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -1516,25 +1516,25 @@
         <v>39</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F28">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G28" s="1">
-        <v>56.41</v>
+        <v>69.23</v>
       </c>
       <c r="H28" s="1">
-        <v>43.59</v>
+        <v>30.77</v>
       </c>
       <c r="I28" s="2">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="J28">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>43.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2723,25 +2723,25 @@
         <v>39</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G28" s="1">
-        <v>51.28</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>48.72</v>
+        <v>35.9</v>
       </c>
       <c r="I28" s="2">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J28">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>43.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3930,25 +3930,25 @@
         <v>39</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G28" s="1">
-        <v>51.28</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>48.72</v>
+        <v>35.9</v>
       </c>
       <c r="I28" s="2">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="J28">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>43.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -3580,19 +3580,19 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>74.19</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>25.81</v>
+        <v>9.68</v>
       </c>
       <c r="I18" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3615,19 +3615,19 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>74.29000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>25.71</v>
+        <v>11.43</v>
       </c>
       <c r="I19" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3650,16 +3650,16 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>95.23999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="H20" s="1">
-        <v>4.76</v>
+        <v>9.52</v>
       </c>
       <c r="I20" s="2">
         <v>6.7</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3720,19 +3720,19 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H22" s="1">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="I22" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3767,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3825,19 +3825,19 @@
         <v>41</v>
       </c>
       <c r="E25">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>51.22</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>48.78</v>
+        <v>7.32</v>
       </c>
       <c r="I25" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3930,19 +3930,19 @@
         <v>39</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G28" s="1">
-        <v>64.09999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="H28" s="1">
-        <v>35.9</v>
+        <v>23.08</v>
       </c>
       <c r="I28" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3965,16 +3965,16 @@
         <v>34</v>
       </c>
       <c r="E29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H29" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I29" s="2">
         <v>7.3</v>
@@ -4000,19 +4000,19 @@
         <v>30</v>
       </c>
       <c r="E30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G30" s="1">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="H30" s="1">
-        <v>16.67</v>
+        <v>10</v>
       </c>
       <c r="I30" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4105,19 +4105,19 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H33" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J33">
         <v>0</v>

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -3440,19 +3440,19 @@
         <v>35</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>74.29000000000001</v>
+        <v>80</v>
       </c>
       <c r="H14" s="1">
-        <v>25.71</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3475,19 +3475,19 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>81.58</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>18.42</v>
+        <v>15.79</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3510,19 +3510,19 @@
         <v>26</v>
       </c>
       <c r="E16">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>69.23</v>
+        <v>80.77</v>
       </c>
       <c r="H16" s="1">
-        <v>30.77</v>
+        <v>19.23</v>
       </c>
       <c r="I16" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3545,19 +3545,19 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H17" s="1">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="I17" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3790,19 +3790,19 @@
         <v>32</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G24" s="1">
-        <v>68.75</v>
+        <v>62.5</v>
       </c>
       <c r="H24" s="1">
-        <v>31.25</v>
+        <v>37.5</v>
       </c>
       <c r="I24" s="2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3860,19 +3860,19 @@
         <v>39</v>
       </c>
       <c r="E26">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G26" s="1">
-        <v>61.54</v>
+        <v>74.36</v>
       </c>
       <c r="H26" s="1">
-        <v>38.46</v>
+        <v>25.64</v>
       </c>
       <c r="I26" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G27" s="1">
-        <v>58.06</v>
+        <v>70.97</v>
       </c>
       <c r="H27" s="1">
-        <v>41.94</v>
+        <v>29.03</v>
       </c>
       <c r="I27" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4035,16 +4035,16 @@
         <v>41</v>
       </c>
       <c r="E31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G31" s="1">
-        <v>82.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H31" s="1">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
       <c r="I31" s="2">
         <v>6.6</v>
@@ -4070,19 +4070,19 @@
         <v>40</v>
       </c>
       <c r="E32">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H32" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I32" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J32">
         <v>0</v>

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -3020,19 +3020,19 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="H2" s="1">
-        <v>38.46</v>
+        <v>30.77</v>
       </c>
       <c r="I2" s="2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3055,19 +3055,19 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>65.38</v>
+        <v>84.62</v>
       </c>
       <c r="H3" s="1">
-        <v>34.62</v>
+        <v>15.38</v>
       </c>
       <c r="I3" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3090,16 +3090,16 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>63.16</v>
+        <v>78.95</v>
       </c>
       <c r="H4" s="1">
-        <v>36.84</v>
+        <v>21.05</v>
       </c>
       <c r="I4" s="2">
         <v>6.8</v>
@@ -3125,16 +3125,16 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>32.35</v>
+        <v>14.71</v>
       </c>
       <c r="I5" s="2">
         <v>6.6</v>
@@ -3160,19 +3160,19 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>77.78</v>
+        <v>94.44</v>
       </c>
       <c r="H6" s="1">
-        <v>22.22</v>
+        <v>5.56</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3195,19 +3195,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="I7" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>84.09</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>15.91</v>
+        <v>6.82</v>
       </c>
       <c r="I8" s="2">
         <v>7.4</v>
@@ -3265,16 +3265,16 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>76.73999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H9" s="1">
-        <v>23.26</v>
+        <v>13.95</v>
       </c>
       <c r="I9" s="2">
         <v>7</v>
@@ -3300,19 +3300,19 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>76.73999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>23.26</v>
+        <v>18.6</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4140,19 +4140,19 @@
         <v>44</v>
       </c>
       <c r="E34">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1">
-        <v>86.36</v>
+        <v>88.64</v>
       </c>
       <c r="H34" s="1">
-        <v>13.64</v>
+        <v>11.36</v>
       </c>
       <c r="I34" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>0</v>

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -3335,16 +3335,16 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>32.35</v>
+        <v>14.71</v>
       </c>
       <c r="I11" s="2">
         <v>6.7</v>

--- a/academias/Matemáticas - Estadisticos 20221.xlsx
+++ b/academias/Matemáticas - Estadisticos 20221.xlsx
@@ -3370,19 +3370,19 @@
         <v>15</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>53.33</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>46.67</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3405,19 +3405,19 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H13" s="1">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="I13" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
